--- a/bom/파이브가이즈_7호점_도면인덱스_20260408.xlsx
+++ b/bom/파이브가이즈_7호점_도면인덱스_20260408.xlsx
@@ -3080,7 +3080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="81" min="1" max="2"/>
@@ -4613,440 +4613,448 @@
       <c r="L28" s="112" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="82">
-      <c r="A29" s="105" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EF-1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>배기휀 1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>동력</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>F-CV 4㎟ 4C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>3Φ 380V (E-003 우측열)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="82">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OAC-2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>실외기2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>동력</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>HFIX 6㎟ 4C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>3Φ 380V</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="82">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OAC-4</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>실외기4</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>동력</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>HFIX 6㎟ 4C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>3Φ 380V</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="82">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SPARE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>예비</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3상 예비</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="82">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CDU-2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CONDENSING UNIT-MEAT REFRIGERATION</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>동력</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 4C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>3Φ 380V 육류냉장</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="82">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ELCB</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DRYER</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>동력</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>F-CV 4㎟ 4C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>3Φ 380V 8.5kW (E-104 EQP LIST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="82">
+      <c r="A35" s="105" t="inlineStr">
         <is>
           <t>LP-E</t>
         </is>
       </c>
-      <c r="B29" s="105" t="inlineStr">
+      <c r="B35" s="105" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="C29" s="105" t="n">
+      <c r="C35" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="105" t="n">
+      <c r="D35" s="105" t="n">
         <v>50</v>
       </c>
-      <c r="E29" s="105" t="n">
+      <c r="E35" s="105" t="n">
         <v>30</v>
       </c>
-      <c r="F29" s="105" t="inlineStr">
+      <c r="F35" s="105" t="inlineStr">
         <is>
           <t>MCCB</t>
         </is>
       </c>
-      <c r="G29" s="106" t="inlineStr">
+      <c r="G35" s="106" t="inlineStr">
         <is>
           <t>MAIN (LP-1M에서 인입)</t>
         </is>
       </c>
-      <c r="H29" s="107" t="inlineStr">
+      <c r="H35" s="107" t="inlineStr">
         <is>
           <t>간선</t>
         </is>
       </c>
-      <c r="I29" s="105" t="inlineStr">
+      <c r="I35" s="105" t="inlineStr">
         <is>
           <t>F-CV 4C</t>
         </is>
       </c>
-      <c r="J29" s="105" t="inlineStr">
+      <c r="J35" s="105" t="inlineStr">
         <is>
           <t>ST 28C</t>
         </is>
       </c>
-      <c r="K29" s="105" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L29" s="106" t="inlineStr">
+      <c r="K35" s="105" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L35" s="106" t="inlineStr">
         <is>
           <t>LP-1M 분기</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="82">
-      <c r="A30" s="88" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="82">
+      <c r="A36" s="88" t="inlineStr">
         <is>
           <t>LP-E</t>
         </is>
       </c>
-      <c r="B30" s="88" t="inlineStr">
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C30" s="88" t="n">
+      <c r="C36" s="88" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="88" t="n">
+      <c r="D36" s="88" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="88" t="n">
+      <c r="E36" s="88" t="n">
         <v>20</v>
       </c>
-      <c r="F30" s="88" t="inlineStr">
+      <c r="F36" s="88" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G30" s="90" t="inlineStr">
+      <c r="G36" s="90" t="inlineStr">
         <is>
           <t>에어커튼</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="H36" s="91" t="inlineStr">
         <is>
           <t>동력</t>
         </is>
       </c>
-      <c r="I30" s="88" t="inlineStr">
+      <c r="I36" s="88" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J30" s="88" t="inlineStr">
+      <c r="J36" s="88" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K30" s="88" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L30" s="89" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="82">
-      <c r="A31" s="92" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B31" s="92" t="inlineStr">
-        <is>
-          <t>ER2</t>
-        </is>
-      </c>
-      <c r="C31" s="92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="92" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="92" t="n">
-        <v>20</v>
-      </c>
-      <c r="F31" s="92" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G31" s="94" t="inlineStr">
-        <is>
-          <t>매니저룸</t>
-        </is>
-      </c>
-      <c r="H31" s="95" t="inlineStr">
-        <is>
-          <t>전열</t>
-        </is>
-      </c>
-      <c r="I31" s="92" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J31" s="92" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K31" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L31" s="93" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="82">
-      <c r="A32" s="92" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B32" s="92" t="inlineStr">
-        <is>
-          <t>ER3</t>
-        </is>
-      </c>
-      <c r="C32" s="92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="92" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" s="92" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="92" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G32" s="94" t="inlineStr">
-        <is>
-          <t>매니저룸(단상RACK)</t>
-        </is>
-      </c>
-      <c r="H32" s="95" t="inlineStr">
-        <is>
-          <t>전열</t>
-        </is>
-      </c>
-      <c r="I32" s="92" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J32" s="92" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K32" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L32" s="93" t="inlineStr">
-        <is>
-          <t>IT 랙</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="82">
-      <c r="A33" s="121" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B33" s="121" t="inlineStr">
-        <is>
-          <t>SP1</t>
-        </is>
-      </c>
-      <c r="C33" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="121" t="n">
-        <v>30</v>
-      </c>
-      <c r="E33" s="121" t="n">
-        <v>20</v>
-      </c>
-      <c r="F33" s="121" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G33" s="122" t="inlineStr">
-        <is>
-          <t>간이 스프링쿨러</t>
-        </is>
-      </c>
-      <c r="H33" s="123" t="inlineStr">
-        <is>
-          <t>소방</t>
-        </is>
-      </c>
-      <c r="I33" s="121" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J33" s="121" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K33" s="121" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L33" s="122" t="inlineStr">
-        <is>
-          <t>사용자 확정</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="82">
-      <c r="A34" s="121" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B34" s="121" t="inlineStr">
-        <is>
-          <t>ER5</t>
-        </is>
-      </c>
-      <c r="C34" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="121" t="n">
-        <v>30</v>
-      </c>
-      <c r="E34" s="121" t="n">
-        <v>20</v>
-      </c>
-      <c r="F34" s="121" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G34" s="122" t="inlineStr">
-        <is>
-          <t>가스경보</t>
-        </is>
-      </c>
-      <c r="H34" s="123" t="inlineStr">
-        <is>
-          <t>소방</t>
-        </is>
-      </c>
-      <c r="I34" s="121" t="inlineStr">
-        <is>
-          <t>HFIX 1.5㎟</t>
-        </is>
-      </c>
-      <c r="J34" s="121" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K34" s="121" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L34" s="122" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="82">
-      <c r="A35" s="121" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B35" s="121" t="inlineStr">
-        <is>
-          <t>EX1</t>
-        </is>
-      </c>
-      <c r="C35" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="121" t="n">
-        <v>30</v>
-      </c>
-      <c r="E35" s="121" t="n">
-        <v>20</v>
-      </c>
-      <c r="F35" s="121" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G35" s="122" t="inlineStr">
-        <is>
-          <t>유도등</t>
-        </is>
-      </c>
-      <c r="H35" s="123" t="inlineStr">
-        <is>
-          <t>소방</t>
-        </is>
-      </c>
-      <c r="I35" s="121" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟</t>
-        </is>
-      </c>
-      <c r="J35" s="121" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K35" s="121" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L35" s="122" t="inlineStr">
-        <is>
-          <t>비상전원</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="82">
-      <c r="A36" s="85" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B36" s="85" t="inlineStr">
-        <is>
-          <t>AD1</t>
-        </is>
-      </c>
-      <c r="C36" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="85" t="n">
-        <v>30</v>
-      </c>
-      <c r="E36" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="F36" s="85" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G36" s="86" t="inlineStr">
-        <is>
-          <t>자동문</t>
-        </is>
-      </c>
-      <c r="H36" s="87" t="inlineStr">
-        <is>
-          <t>제어</t>
-        </is>
-      </c>
-      <c r="I36" s="85" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J36" s="85" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K36" s="85" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L36" s="86" t="inlineStr">
-        <is>
-          <t>사용자 확정</t>
-        </is>
-      </c>
+      <c r="K36" s="88" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L36" s="89" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="82">
       <c r="A37" s="92" t="inlineStr">
@@ -5056,7 +5064,7 @@
       </c>
       <c r="B37" s="92" t="inlineStr">
         <is>
-          <t>ET1</t>
+          <t>ER2</t>
         </is>
       </c>
       <c r="C37" s="92" t="n">
@@ -5073,9 +5081,9 @@
           <t>ELB</t>
         </is>
       </c>
-      <c r="G37" s="93" t="inlineStr">
-        <is>
-          <t>1층 화장실 온수기</t>
+      <c r="G37" s="94" t="inlineStr">
+        <is>
+          <t>매니저룸</t>
         </is>
       </c>
       <c r="H37" s="95" t="inlineStr">
@@ -5108,7 +5116,7 @@
       </c>
       <c r="B38" s="92" t="inlineStr">
         <is>
-          <t>EH1</t>
+          <t>ER3</t>
         </is>
       </c>
       <c r="C38" s="92" t="n">
@@ -5125,410 +5133,422 @@
           <t>ELB</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="G38" s="94" t="inlineStr">
+        <is>
+          <t>매니저룸(단상RACK)</t>
+        </is>
+      </c>
+      <c r="H38" s="95" t="inlineStr">
+        <is>
+          <t>전열</t>
+        </is>
+      </c>
+      <c r="I38" s="92" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J38" s="92" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K38" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L38" s="93" t="inlineStr">
+        <is>
+          <t>IT 랙</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="82">
+      <c r="A39" s="121" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B39" s="121" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="121" t="n">
+        <v>30</v>
+      </c>
+      <c r="E39" s="121" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="121" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G39" s="122" t="inlineStr">
+        <is>
+          <t>간이 스프링쿨러</t>
+        </is>
+      </c>
+      <c r="H39" s="123" t="inlineStr">
+        <is>
+          <t>소방</t>
+        </is>
+      </c>
+      <c r="I39" s="121" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J39" s="121" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K39" s="121" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L39" s="122" t="inlineStr">
+        <is>
+          <t>사용자 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="82">
+      <c r="A40" s="121" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B40" s="121" t="inlineStr">
+        <is>
+          <t>ER5</t>
+        </is>
+      </c>
+      <c r="C40" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="121" t="n">
+        <v>30</v>
+      </c>
+      <c r="E40" s="121" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" s="121" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G40" s="122" t="inlineStr">
+        <is>
+          <t>가스경보</t>
+        </is>
+      </c>
+      <c r="H40" s="123" t="inlineStr">
+        <is>
+          <t>소방</t>
+        </is>
+      </c>
+      <c r="I40" s="121" t="inlineStr">
+        <is>
+          <t>HFIX 1.5㎟</t>
+        </is>
+      </c>
+      <c r="J40" s="121" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K40" s="121" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L40" s="122" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="82">
+      <c r="A41" s="121" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B41" s="121" t="inlineStr">
+        <is>
+          <t>EX1</t>
+        </is>
+      </c>
+      <c r="C41" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="121" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" s="121" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="121" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G41" s="122" t="inlineStr">
+        <is>
+          <t>유도등</t>
+        </is>
+      </c>
+      <c r="H41" s="123" t="inlineStr">
+        <is>
+          <t>소방</t>
+        </is>
+      </c>
+      <c r="I41" s="121" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟</t>
+        </is>
+      </c>
+      <c r="J41" s="121" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K41" s="121" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L41" s="122" t="inlineStr">
+        <is>
+          <t>비상전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="82">
+      <c r="A42" s="85" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B42" s="85" t="inlineStr">
+        <is>
+          <t>AD1</t>
+        </is>
+      </c>
+      <c r="C42" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="85" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="F42" s="85" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G42" s="86" t="inlineStr">
+        <is>
+          <t>자동문</t>
+        </is>
+      </c>
+      <c r="H42" s="87" t="inlineStr">
+        <is>
+          <t>제어</t>
+        </is>
+      </c>
+      <c r="I42" s="85" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J42" s="85" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K42" s="85" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L42" s="86" t="inlineStr">
+        <is>
+          <t>사용자 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="82">
+      <c r="A43" s="92" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B43" s="92" t="inlineStr">
+        <is>
+          <t>ET1</t>
+        </is>
+      </c>
+      <c r="C43" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="92" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="92" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" s="92" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G43" s="93" t="inlineStr">
+        <is>
+          <t>1층 화장실 온수기</t>
+        </is>
+      </c>
+      <c r="H43" s="95" t="inlineStr">
+        <is>
+          <t>전열</t>
+        </is>
+      </c>
+      <c r="I43" s="92" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J43" s="92" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K43" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L43" s="93" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="82">
+      <c r="A44" s="92" t="inlineStr">
+        <is>
+          <t>LP-E</t>
+        </is>
+      </c>
+      <c r="B44" s="92" t="inlineStr">
+        <is>
+          <t>EH1</t>
+        </is>
+      </c>
+      <c r="C44" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="92" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="92" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" s="92" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G44" s="93" t="inlineStr">
         <is>
           <t>1층 화장실 히터</t>
         </is>
       </c>
-      <c r="H38" s="95" t="inlineStr">
+      <c r="H44" s="95" t="inlineStr">
         <is>
           <t>전열</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="I44" s="92" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="J44" s="92" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L38" s="93" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="82">
-      <c r="A39" s="118" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B39" s="118" t="inlineStr">
+      <c r="K44" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L44" s="93" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="82">
+      <c r="A45" s="118" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B45" s="118" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C39" s="118" t="n">
+      <c r="C45" s="118" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="118" t="n">
+      <c r="D45" s="118" t="n">
         <v>30</v>
       </c>
-      <c r="E39" s="118" t="n">
+      <c r="E45" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="F39" s="118" t="inlineStr">
+      <c r="F45" s="118" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G39" s="119" t="inlineStr">
+      <c r="G45" s="119" t="inlineStr">
         <is>
           <t>실내기전원</t>
         </is>
       </c>
-      <c r="H39" s="120" t="inlineStr">
+      <c r="H45" s="120" t="inlineStr">
         <is>
           <t>공조</t>
         </is>
       </c>
-      <c r="I39" s="118" t="inlineStr">
+      <c r="I45" s="118" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J39" s="118" t="inlineStr">
+      <c r="J45" s="118" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K39" s="118" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L39" s="119" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="82">
-      <c r="A40" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B40" s="98" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="C40" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E40" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F40" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G40" s="99" t="inlineStr">
-        <is>
-          <t>POTATO SINK</t>
-        </is>
-      </c>
-      <c r="H40" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I40" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J40" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K40" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L40" s="99" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="82">
-      <c r="A41" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B41" s="98" t="inlineStr">
-        <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="C41" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G41" s="99" t="inlineStr">
-        <is>
-          <t>FRYER, 4BAY (GAS TYPE) × 2</t>
-        </is>
-      </c>
-      <c r="H41" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I41" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J41" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K41" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L41" s="100" t="inlineStr">
-        <is>
-          <t>점화/제어 전원</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="82">
-      <c r="A42" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B42" s="98" t="inlineStr">
-        <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C42" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E42" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F42" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G42" s="99" t="inlineStr">
-        <is>
-          <t>SANDWICH WRAP TABLE/PREP TABLE</t>
-        </is>
-      </c>
-      <c r="H42" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I42" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J42" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K42" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L42" s="99" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="82">
-      <c r="A43" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B43" s="98" t="inlineStr">
-        <is>
-          <t>K8</t>
-        </is>
-      </c>
-      <c r="C43" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F43" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G43" s="99" t="inlineStr">
-        <is>
-          <t>COOKED FRIED STATION/FRY STATION TABLE W/WARMER</t>
-        </is>
-      </c>
-      <c r="H43" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I43" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J43" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K43" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L43" s="99" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="82">
-      <c r="A44" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B44" s="98" t="inlineStr">
-        <is>
-          <t>K10</t>
-        </is>
-      </c>
-      <c r="C44" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F44" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G44" s="99" t="inlineStr">
-        <is>
-          <t>SHAKE FOUNTAINETTE COOLER/ORDER PRINTER</t>
-        </is>
-      </c>
-      <c r="H44" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I44" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J44" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K44" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L44" s="99" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="82">
-      <c r="A45" s="98" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B45" s="98" t="inlineStr">
-        <is>
-          <t>K12</t>
-        </is>
-      </c>
-      <c r="C45" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="E45" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="F45" s="98" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G45" s="99" t="inlineStr">
-        <is>
-          <t>FOUNTAIN DISPENSER</t>
-        </is>
-      </c>
-      <c r="H45" s="101" t="inlineStr">
-        <is>
-          <t>주방기기</t>
-        </is>
-      </c>
-      <c r="I45" s="98" t="inlineStr">
-        <is>
-          <t>HFIX 4㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J45" s="98" t="inlineStr">
-        <is>
-          <t>ST 22C</t>
-        </is>
-      </c>
-      <c r="K45" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L45" s="99" t="n"/>
+      <c r="K45" s="118" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L45" s="119" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="82">
       <c r="A46" s="98" t="inlineStr">
         <is>
-          <t>LP-E</t>
+          <t>LP-1M</t>
         </is>
       </c>
       <c r="B46" s="98" t="inlineStr">
         <is>
-          <t>K14</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C46" s="98" t="n">
@@ -5547,7 +5567,7 @@
       </c>
       <c r="G46" s="99" t="inlineStr">
         <is>
-          <t>FOUNTAIN DISPENSER</t>
+          <t>POTATO SINK</t>
         </is>
       </c>
       <c r="H46" s="101" t="inlineStr">
@@ -5575,12 +5595,12 @@
     <row r="47" ht="15" customHeight="1" s="82">
       <c r="A47" s="98" t="inlineStr">
         <is>
-          <t>LP-E</t>
+          <t>LP-1M</t>
         </is>
       </c>
       <c r="B47" s="98" t="inlineStr">
         <is>
-          <t>K16</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C47" s="98" t="n">
@@ -5599,507 +5619,507 @@
       </c>
       <c r="G47" s="99" t="inlineStr">
         <is>
+          <t>FRYER, 4BAY (GAS TYPE) × 2</t>
+        </is>
+      </c>
+      <c r="H47" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I47" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J47" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K47" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L47" s="100" t="inlineStr">
+        <is>
+          <t>점화/제어 전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="82">
+      <c r="A48" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B48" s="98" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C48" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G48" s="99" t="inlineStr">
+        <is>
+          <t>SANDWICH WRAP TABLE/PREP TABLE</t>
+        </is>
+      </c>
+      <c r="H48" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I48" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J48" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K48" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L48" s="99" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="82">
+      <c r="A49" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B49" s="98" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C49" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E49" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G49" s="99" t="inlineStr">
+        <is>
+          <t>COOKED FRIED STATION/FRY STATION TABLE W/WARMER</t>
+        </is>
+      </c>
+      <c r="H49" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I49" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J49" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K49" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L49" s="99" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="82">
+      <c r="A50" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B50" s="98" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C50" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E50" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G50" s="99" t="inlineStr">
+        <is>
+          <t>SHAKE FOUNTAINETTE COOLER/ORDER PRINTER</t>
+        </is>
+      </c>
+      <c r="H50" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I50" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J50" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K50" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L50" s="99" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="82">
+      <c r="A51" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B51" s="98" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C51" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E51" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G51" s="99" t="inlineStr">
+        <is>
+          <t>FOUNTAIN DISPENSER</t>
+        </is>
+      </c>
+      <c r="H51" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I51" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J51" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K51" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L51" s="99" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="82">
+      <c r="A52" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B52" s="98" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+      <c r="C52" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E52" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G52" s="99" t="inlineStr">
+        <is>
+          <t>FOUNTAIN DISPENSER</t>
+        </is>
+      </c>
+      <c r="H52" s="101" t="inlineStr">
+        <is>
+          <t>주방기기</t>
+        </is>
+      </c>
+      <c r="I52" s="98" t="inlineStr">
+        <is>
+          <t>HFIX 4㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J52" s="98" t="inlineStr">
+        <is>
+          <t>ST 22C</t>
+        </is>
+      </c>
+      <c r="K52" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L52" s="99" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="82">
+      <c r="A53" s="98" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B53" s="98" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="C53" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="E53" s="98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="98" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G53" s="99" t="inlineStr">
+        <is>
           <t>Water Booster</t>
         </is>
       </c>
-      <c r="H47" s="101" t="inlineStr">
+      <c r="H53" s="101" t="inlineStr">
         <is>
           <t>주방기기</t>
         </is>
       </c>
-      <c r="I47" s="98" t="inlineStr">
+      <c r="I53" s="98" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J47" s="98" t="inlineStr">
+      <c r="J53" s="98" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K47" s="98" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L47" s="99" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="82">
-      <c r="A48" s="92" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B48" s="92" t="inlineStr">
+      <c r="K53" s="98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L53" s="99" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="82">
+      <c r="A54" s="92" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B54" s="92" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="C48" s="92" t="n">
+      <c r="C54" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="92" t="n">
+      <c r="D54" s="92" t="n">
         <v>30</v>
       </c>
-      <c r="E48" s="92" t="n">
+      <c r="E54" s="92" t="n">
         <v>20</v>
       </c>
-      <c r="F48" s="92" t="inlineStr">
+      <c r="F54" s="92" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G48" s="94" t="inlineStr">
+      <c r="G54" s="94" t="inlineStr">
         <is>
           <t>매니저룸</t>
         </is>
       </c>
-      <c r="H48" s="95" t="inlineStr">
+      <c r="H54" s="95" t="inlineStr">
         <is>
           <t>전열</t>
         </is>
       </c>
-      <c r="I48" s="92" t="inlineStr">
+      <c r="I54" s="92" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J48" s="92" t="inlineStr">
+      <c r="J54" s="92" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K48" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L48" s="93" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="82">
-      <c r="A49" s="92" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B49" s="92" t="inlineStr">
+      <c r="K54" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L54" s="93" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="82">
+      <c r="A55" s="92" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B55" s="92" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="C49" s="92" t="n">
+      <c r="C55" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="D49" s="92" t="n">
+      <c r="D55" s="92" t="n">
         <v>30</v>
       </c>
-      <c r="E49" s="92" t="n">
+      <c r="E55" s="92" t="n">
         <v>20</v>
       </c>
-      <c r="F49" s="92" t="inlineStr">
+      <c r="F55" s="92" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G49" s="94" t="inlineStr">
+      <c r="G55" s="94" t="inlineStr">
         <is>
           <t>포중등/MIC외</t>
         </is>
       </c>
-      <c r="H49" s="95" t="inlineStr">
+      <c r="H55" s="95" t="inlineStr">
         <is>
           <t>전열</t>
         </is>
       </c>
-      <c r="I49" s="92" t="inlineStr">
+      <c r="I55" s="92" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J49" s="92" t="inlineStr">
+      <c r="J55" s="92" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K49" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L49" s="93" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="82">
-      <c r="A50" s="92" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B50" s="92" t="inlineStr">
+      <c r="K55" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L55" s="93" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="82">
+      <c r="A56" s="92" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B56" s="92" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="C50" s="92" t="n">
+      <c r="C56" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="92" t="n">
+      <c r="D56" s="92" t="n">
         <v>30</v>
       </c>
-      <c r="E50" s="92" t="n">
+      <c r="E56" s="92" t="n">
         <v>20</v>
       </c>
-      <c r="F50" s="92" t="inlineStr">
+      <c r="F56" s="92" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G50" s="94" t="inlineStr">
+      <c r="G56" s="94" t="inlineStr">
         <is>
           <t>포중등/정수기/핸드믹서</t>
         </is>
       </c>
-      <c r="H50" s="95" t="inlineStr">
+      <c r="H56" s="95" t="inlineStr">
         <is>
           <t>전열</t>
         </is>
       </c>
-      <c r="I50" s="92" t="inlineStr">
+      <c r="I56" s="92" t="inlineStr">
         <is>
           <t>HFIX 4㎟ 3C</t>
         </is>
       </c>
-      <c r="J50" s="92" t="inlineStr">
+      <c r="J56" s="92" t="inlineStr">
         <is>
           <t>ST 22C</t>
         </is>
       </c>
-      <c r="K50" s="92" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L50" s="93" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="82">
-      <c r="A51" s="111" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B51" s="111" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="C51" s="111" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" s="111" t="n">
-        <v>30</v>
-      </c>
-      <c r="E51" s="111" t="n">
-        <v>20</v>
-      </c>
-      <c r="F51" s="111" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G51" s="112" t="inlineStr">
-        <is>
-          <t>SPARE</t>
-        </is>
-      </c>
-      <c r="H51" s="113" t="inlineStr">
-        <is>
-          <t>예비</t>
-        </is>
-      </c>
-      <c r="I51" s="111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="111" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L51" s="112" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="82">
-      <c r="A52" s="96" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B52" s="96" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C52" s="96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="96" t="n">
-        <v>30</v>
-      </c>
-      <c r="E52" s="96" t="n">
-        <v>20</v>
-      </c>
-      <c r="F52" s="96" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G52" s="97" t="inlineStr">
-        <is>
-          <t>LIGHTING</t>
-        </is>
-      </c>
-      <c r="H52" s="115" t="inlineStr">
-        <is>
-          <t>조명</t>
-        </is>
-      </c>
-      <c r="I52" s="96" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J52" s="96" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K52" s="96" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L52" s="97" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="82">
-      <c r="A53" s="118" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B53" s="118" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C53" s="118" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="118" t="n">
-        <v>30</v>
-      </c>
-      <c r="E53" s="118" t="n">
-        <v>20</v>
-      </c>
-      <c r="F53" s="118" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G53" s="124" t="inlineStr">
-        <is>
-          <t>HOOD/LAMP/FILTER × 5</t>
-        </is>
-      </c>
-      <c r="H53" s="120" t="inlineStr">
-        <is>
-          <t>공조</t>
-        </is>
-      </c>
-      <c r="I53" s="118" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J53" s="118" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K53" s="118" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L53" s="119" t="inlineStr">
-        <is>
-          <t>후드 5조</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="82">
-      <c r="A54" s="118" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B54" s="118" t="inlineStr">
-        <is>
-          <t>ERV2</t>
-        </is>
-      </c>
-      <c r="C54" s="118" t="n">
-        <v>2</v>
-      </c>
-      <c r="D54" s="118" t="n">
-        <v>30</v>
-      </c>
-      <c r="E54" s="118" t="n">
-        <v>20</v>
-      </c>
-      <c r="F54" s="118" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G54" s="119" t="inlineStr">
-        <is>
-          <t>전열교환기2</t>
-        </is>
-      </c>
-      <c r="H54" s="120" t="inlineStr">
-        <is>
-          <t>공조</t>
-        </is>
-      </c>
-      <c r="I54" s="118" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J54" s="118" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K54" s="118" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L54" s="124" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="82">
-      <c r="A55" s="85" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B55" s="85" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="C55" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="85" t="n">
-        <v>30</v>
-      </c>
-      <c r="E55" s="85" t="n">
-        <v>20</v>
-      </c>
-      <c r="F55" s="85" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G55" s="117" t="inlineStr">
-        <is>
-          <t>SIGN</t>
-        </is>
-      </c>
-      <c r="H55" s="87" t="inlineStr">
-        <is>
-          <t>사인</t>
-        </is>
-      </c>
-      <c r="I55" s="85" t="inlineStr">
-        <is>
-          <t>HFIX 2.5㎟ 3C</t>
-        </is>
-      </c>
-      <c r="J55" s="85" t="inlineStr">
-        <is>
-          <t>ST 16C</t>
-        </is>
-      </c>
-      <c r="K55" s="85" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L55" s="117" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="82">
-      <c r="A56" s="111" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B56" s="111" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="C56" s="111" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="111" t="n">
-        <v>30</v>
-      </c>
-      <c r="E56" s="111" t="n">
-        <v>20</v>
-      </c>
-      <c r="F56" s="111" t="inlineStr">
-        <is>
-          <t>ELB</t>
-        </is>
-      </c>
-      <c r="G56" s="112" t="inlineStr">
-        <is>
-          <t>SPARE</t>
-        </is>
-      </c>
-      <c r="H56" s="113" t="inlineStr">
-        <is>
-          <t>예비</t>
-        </is>
-      </c>
-      <c r="I56" s="111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="111" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L56" s="112" t="n"/>
+      <c r="K56" s="92" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L56" s="93" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="82">
       <c r="A57" s="111" t="inlineStr">
         <is>
-          <t>LP-E</t>
+          <t>LP-1M</t>
         </is>
       </c>
       <c r="B57" s="111" t="inlineStr">
@@ -6149,56 +6169,372 @@
       <c r="L57" s="112" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="82">
-      <c r="A58" s="111" t="inlineStr">
-        <is>
-          <t>LP-E</t>
-        </is>
-      </c>
-      <c r="B58" s="111" t="inlineStr">
+      <c r="A58" s="96" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B58" s="96" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C58" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="96" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" s="96" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="96" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G58" s="97" t="inlineStr">
+        <is>
+          <t>LIGHTING</t>
+        </is>
+      </c>
+      <c r="H58" s="115" t="inlineStr">
+        <is>
+          <t>조명</t>
+        </is>
+      </c>
+      <c r="I58" s="96" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J58" s="96" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K58" s="96" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L58" s="97" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="118" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B59" s="118" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C59" s="118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="118" t="n">
+        <v>30</v>
+      </c>
+      <c r="E59" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" s="118" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G59" s="124" t="inlineStr">
+        <is>
+          <t>HOOD/LAMP/FILTER × 5</t>
+        </is>
+      </c>
+      <c r="H59" s="120" t="inlineStr">
+        <is>
+          <t>공조</t>
+        </is>
+      </c>
+      <c r="I59" s="118" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J59" s="118" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K59" s="118" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L59" s="119" t="inlineStr">
+        <is>
+          <t>후드 5조</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="118" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B60" s="118" t="inlineStr">
+        <is>
+          <t>ERV2</t>
+        </is>
+      </c>
+      <c r="C60" s="118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="118" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" s="118" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G60" s="119" t="inlineStr">
+        <is>
+          <t>전열교환기2</t>
+        </is>
+      </c>
+      <c r="H60" s="120" t="inlineStr">
+        <is>
+          <t>공조</t>
+        </is>
+      </c>
+      <c r="I60" s="118" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J60" s="118" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K60" s="118" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L60" s="124" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="85" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B61" s="85" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C61" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="85" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" s="85" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="85" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G61" s="117" t="inlineStr">
+        <is>
+          <t>SIGN</t>
+        </is>
+      </c>
+      <c r="H61" s="87" t="inlineStr">
+        <is>
+          <t>사인</t>
+        </is>
+      </c>
+      <c r="I61" s="85" t="inlineStr">
+        <is>
+          <t>HFIX 2.5㎟ 3C</t>
+        </is>
+      </c>
+      <c r="J61" s="85" t="inlineStr">
+        <is>
+          <t>ST 16C</t>
+        </is>
+      </c>
+      <c r="K61" s="85" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L61" s="117" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="111" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B62" s="111" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="C58" s="111" t="n">
+      <c r="C62" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="D58" s="111" t="n">
+      <c r="D62" s="111" t="n">
         <v>30</v>
       </c>
-      <c r="E58" s="111" t="n">
+      <c r="E62" s="111" t="n">
         <v>20</v>
       </c>
-      <c r="F58" s="111" t="inlineStr">
+      <c r="F62" s="111" t="inlineStr">
         <is>
           <t>ELB</t>
         </is>
       </c>
-      <c r="G58" s="112" t="inlineStr">
+      <c r="G62" s="112" t="inlineStr">
         <is>
           <t>SPARE</t>
         </is>
       </c>
-      <c r="H58" s="113" t="inlineStr">
+      <c r="H62" s="113" t="inlineStr">
         <is>
           <t>예비</t>
         </is>
       </c>
-      <c r="I58" s="111" t="inlineStr">
+      <c r="I62" s="111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J58" s="111" t="inlineStr">
+      <c r="J62" s="111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K58" s="111" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L58" s="112" t="n"/>
+      <c r="K62" s="111" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L62" s="112" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="111" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B63" s="111" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C63" s="111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="111" t="n">
+        <v>30</v>
+      </c>
+      <c r="E63" s="111" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" s="111" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G63" s="112" t="inlineStr">
+        <is>
+          <t>SPARE</t>
+        </is>
+      </c>
+      <c r="H63" s="113" t="inlineStr">
+        <is>
+          <t>예비</t>
+        </is>
+      </c>
+      <c r="I63" s="111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="111" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L63" s="112" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="111" t="inlineStr">
+        <is>
+          <t>LP-1M</t>
+        </is>
+      </c>
+      <c r="B64" s="111" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C64" s="111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="111" t="n">
+        <v>30</v>
+      </c>
+      <c r="E64" s="111" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" s="111" t="inlineStr">
+        <is>
+          <t>ELB</t>
+        </is>
+      </c>
+      <c r="G64" s="112" t="inlineStr">
+        <is>
+          <t>SPARE</t>
+        </is>
+      </c>
+      <c r="H64" s="113" t="inlineStr">
+        <is>
+          <t>예비</t>
+        </is>
+      </c>
+      <c r="I64" s="111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="111" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L64" s="112" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
